--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.46463614819936</v>
+        <v>3.000503374082396</v>
       </c>
       <c r="D2" t="n">
-        <v>21.1085853966209</v>
+        <v>3.430145126950896</v>
       </c>
       <c r="E2" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F2" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.233964055631</v>
+        <v>4.588019159040037</v>
       </c>
       <c r="D3" t="n">
-        <v>26.3724889047185</v>
+        <v>4.285529447016756</v>
       </c>
       <c r="E3" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F3" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.42217182830807</v>
+        <v>5.918602922100061</v>
       </c>
       <c r="D4" t="n">
-        <v>35.14848311295421</v>
+        <v>5.711628505855059</v>
       </c>
       <c r="E4" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F4" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.22846674417739</v>
+        <v>1.824625845928826</v>
       </c>
       <c r="D5" t="n">
-        <v>9.368361931398777</v>
+        <v>1.522358813852301</v>
       </c>
       <c r="E5" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F5" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.54984326139834</v>
+        <v>8.701849529977229</v>
       </c>
       <c r="D6" t="n">
-        <v>51.6898000310987</v>
+        <v>8.399592505053539</v>
       </c>
       <c r="E6" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F6" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.82777613954077</v>
+        <v>5.172013622675375</v>
       </c>
       <c r="D7" t="n">
-        <v>14.57742447251324</v>
+        <v>2.368831476783401</v>
       </c>
       <c r="E7" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F7" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.01931689705267</v>
+        <v>4.228138995771059</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87414168471479</v>
+        <v>4.529548023766154</v>
       </c>
       <c r="E8" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F8" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.84332706124059</v>
+        <v>7.774540647451596</v>
       </c>
       <c r="D9" t="n">
-        <v>46.76013521079044</v>
+        <v>7.598521971753447</v>
       </c>
       <c r="E9" t="n">
-        <v>13.22346387446235</v>
+        <v>2.148812879600131</v>
       </c>
       <c r="F9" t="n">
-        <v>13.83749366343362</v>
+        <v>2.248592720307964</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
